--- a/table_4_feature_selection.xlsx
+++ b/table_4_feature_selection.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,736 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Признак</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ANOVA_F</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Mutual_Info</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Важность (по обеим метрикам)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>egemaps_50_F2amplitudeLogRelF0_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Средняя (1.58)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Лучшая (0.0438)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Информативен, но хуже по ANOVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>egemaps_22_mfcc1_sma3_amean</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Средняя (1.43)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Слабая связь</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hnr_std</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Низкая (0.51)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Слабая связь</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mean_pitch</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Низкая (0.38)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Слабая связь</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>formant_f3_cv</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Низкая (0.37)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Слабая связь</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>egemaps_87_equivalentSoundLevel_dBp</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Низкая (0.22)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Лучшая (0.0699)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Информативен, но хуже по ANOVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>voicing_ratio</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Высокая (8.18)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Только линейная связь</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>egemaps_28_mfcc4_sma3_amean</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Высокая (7.81)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Хорошая (0.0396)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Лучший компромисс</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>egemaps_65_slopeV500-1500_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Высокая (6.92)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Есть (0.0114)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Лучший компромисс</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>min_pitch</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Высокая (5.80)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Есть (0.0112)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Лучший компромисс</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>formant_f2_cv</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Высокая (5.39)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Только линейная связь</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>formant_f2_mean</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Высокая (5.30)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Слабая (0.0013)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Слабая связь</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>total_duration</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Высокая (5.02)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Лучшая (0.1072)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Лучший компромисс</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>pitch_range</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Высокая (4.95)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Слабая (0.0072)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Слабая связь</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>formant_f1_mean</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Высокая (4.33)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Хорошая (0.0361)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Лучший компромисс</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>max_pitch</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Высокая (4.03)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Слабая (0.0045)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Слабая связь</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>egemaps_44_F1amplitudeLogRelF0_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Высокая (3.70)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Слабая (0.0029)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Слабая связь</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>egemaps_45_F1amplitudeLogRelF0_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Высокая (3.61)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Слабая (0.0007)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Слабая связь</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>egemaps_56_F3amplitudeLogRelF0_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Высокая (3.47)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Лучшая (0.0427)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Лучший компромисс</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>hnr_mean</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Высокая (3.18)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Слабая (0.0009)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Слабая связь</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>egemaps_58_alphaRatioV_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Высокая (21.94)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Лучшая (0.1066)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Лучший компромисс</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>spectral_rolloff</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Высокая (21.94)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Лучшая (0.1066)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Лучший компромисс</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>formant_f3_mean</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Высокая (2.80)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Лучшая (0.0518)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Лучший компромисс</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>egemaps_38_logRelF0-H1-A3_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Высокая (2.79)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Лучшая (0.0425)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Лучший компромисс</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>egemaps_57_F3amplitudeLogRelF0_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Высокая (2.79)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Лучшая (0.0425)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Лучший компромисс</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>std_pitch</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Высокая (2.16)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Лучшая (0.1039)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Лучший компромисс</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>egemaps_48_F2bandwidth_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Высокая (2.15)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Есть (0.0291)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Лучший компромисс</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>egemaps_51_F2amplitudeLogRelF0_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Высокая (2.09)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Слабая (0.0076)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Слабая связь</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>spectral_centroid</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Высокая (19.40)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Лучшая (0.0457)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Лучший компромисс</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>egemaps_24_mfcc2_sma3_amean</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Высокая (13.14)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Лучшая (0.1129)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Лучший компромисс</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>zero_crossing_rate</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Высокая (12.34)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Хорошая (0.0341)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Лучший компромисс</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>formant_f1_cv</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Высокая (10.11)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Только линейная связь</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>